--- a/data/trans_orig/P6601-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6601-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2007</t>
+          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2007 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137655</t>
+          <t>137885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174837</t>
+          <t>176910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93376</t>
+          <t>93165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116939</t>
+          <t>117167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>238316</t>
+          <t>237583</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284721</t>
+          <t>284412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75827</t>
+          <t>75536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112951</t>
+          <t>110090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29164</t>
+          <t>29760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52385</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113512</t>
+          <t>114060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154287</t>
+          <t>153606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105337</t>
+          <t>106364</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142230</t>
+          <t>142582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115953</t>
+          <t>114010</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155788</t>
+          <t>154964</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>245185</t>
+          <t>247280</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>295745</t>
+          <t>295252</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177498</t>
+          <t>177437</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>207361</t>
+          <t>207072</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>435519</t>
+          <t>435642</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>492873</t>
+          <t>493000</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128155</t>
+          <t>128587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172343</t>
+          <t>171109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,49 +1430,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>46070</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34386</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>61379</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>12,84%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>22,93%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>46070</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33999</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>59485</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>179</t>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170420</t>
+          <t>171455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224213</t>
+          <t>222859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>76981</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114174</t>
+          <t>112437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28201</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92467</t>
+          <t>92011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132162</t>
+          <t>130473</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33112</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42810</t>
+          <t>42274</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73454</t>
+          <t>72998</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195659</t>
+          <t>194886</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235903</t>
+          <t>237385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162305</t>
+          <t>161816</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184504</t>
+          <t>184158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364123</t>
+          <t>366042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416365</t>
+          <t>414051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>77636</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111860</t>
+          <t>111200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22512</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42778</t>
+          <t>42917</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>103663</t>
+          <t>106208</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144861</t>
+          <t>147117</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48072</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78325</t>
+          <t>78977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>53320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84053</t>
+          <t>83629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47255</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49423</t>
+          <t>48908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>280366</t>
+          <t>281341</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>324589</t>
+          <t>326027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>287375</t>
+          <t>288021</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>321132</t>
+          <t>320569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>578726</t>
+          <t>578440</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>638469</t>
+          <t>637392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95997</t>
+          <t>95947</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132317</t>
+          <t>133458</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>39800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67022</t>
+          <t>65903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142551</t>
+          <t>142829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>192023</t>
+          <t>189540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79714</t>
+          <t>79557</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>114926</t>
+          <t>116276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>30242</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>95728</t>
+          <t>96600</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>134911</t>
+          <t>138482</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>31320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55952</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41258</t>
+          <t>41255</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69704</t>
+          <t>69380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>902353</t>
+          <t>905606</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>991278</t>
+          <t>989497</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>750565</t>
+          <t>749087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>804559</t>
+          <t>804365</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1672290</t>
+          <t>1667353</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1780456</t>
+          <t>1779671</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>412684</t>
+          <t>412508</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>491194</t>
+          <t>486650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146034</t>
+          <t>147116</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>195215</t>
+          <t>193432</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>572847</t>
+          <t>572741</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>662668</t>
+          <t>664860</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>340713</t>
+          <t>341730</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>408682</t>
+          <t>411617</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40334</t>
+          <t>39795</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69288</t>
+          <t>69630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>394420</t>
+          <t>395090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>470872</t>
+          <t>471829</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>115460</t>
+          <t>113754</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>161627</t>
+          <t>158680</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>33900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>134714</t>
+          <t>135220</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>183921</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2012</t>
+          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85057</t>
+          <t>85210</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116757</t>
+          <t>117813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81734</t>
+          <t>81544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107661</t>
+          <t>107252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175376</t>
+          <t>173729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217515</t>
+          <t>216711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73882</t>
+          <t>74138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106589</t>
+          <t>105397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42239</t>
+          <t>43485</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>67909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123212</t>
+          <t>124439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163251</t>
+          <t>164110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>41219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67493</t>
+          <t>67645</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18570</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49659</t>
+          <t>50034</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79090</t>
+          <t>79503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37904</t>
+          <t>37663</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>40364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>171138</t>
+          <t>169395</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>213755</t>
+          <t>212182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138768</t>
+          <t>139451</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>173863</t>
+          <t>171831</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>322601</t>
+          <t>320100</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>379031</t>
+          <t>374273</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102152</t>
+          <t>102540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139284</t>
+          <t>141745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64010</t>
+          <t>65726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95799</t>
+          <t>98311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176089</t>
+          <t>175459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>226594</t>
+          <t>223952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53873</t>
+          <t>55581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85830</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15361</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74321</t>
+          <t>76446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111279</t>
+          <t>110603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41978</t>
+          <t>41111</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>29577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>54750</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130586</t>
+          <t>129413</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167305</t>
+          <t>167546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120805</t>
+          <t>119677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149278</t>
+          <t>149832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260592</t>
+          <t>257980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309282</t>
+          <t>308777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86368</t>
+          <t>85375</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121556</t>
+          <t>121864</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39606</t>
+          <t>39322</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65632</t>
+          <t>65966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>133097</t>
+          <t>135156</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>180674</t>
+          <t>179147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38804</t>
+          <t>37654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65864</t>
+          <t>64614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50322</t>
+          <t>52309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83266</t>
+          <t>83364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>30891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>43126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>171672</t>
+          <t>170675</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>212747</t>
+          <t>210974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159188</t>
+          <t>159118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194521</t>
+          <t>193705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>339762</t>
+          <t>336901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>396030</t>
+          <t>393573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96615</t>
+          <t>98493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134176</t>
+          <t>136226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70620</t>
+          <t>70531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101082</t>
+          <t>102322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175080</t>
+          <t>176753</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>226188</t>
+          <t>226749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65894</t>
+          <t>65346</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97852</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31018</t>
+          <t>31675</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>82010</t>
+          <t>83015</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120123</t>
+          <t>121863</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44086</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>27942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36888</t>
+          <t>36689</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65353</t>
+          <t>65256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>594194</t>
+          <t>591739</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>670938</t>
+          <t>667742</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>534771</t>
+          <t>530004</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>595774</t>
+          <t>594378</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1145562</t>
+          <t>1146174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1249715</t>
+          <t>1249935</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>394590</t>
+          <t>396439</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>467895</t>
+          <t>464727</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>243247</t>
+          <t>245932</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>301895</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>654786</t>
+          <t>657114</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>752262</t>
+          <t>748090</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>222216</t>
+          <t>225440</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>280834</t>
+          <t>287031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54905</t>
+          <t>55300</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88206</t>
+          <t>88292</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289347</t>
+          <t>290409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>357473</t>
+          <t>356099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>85233</t>
+          <t>84054</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>127540</t>
+          <t>128260</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>30160</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>57533</t>
+          <t>56233</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>119846</t>
+          <t>123764</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>170328</t>
+          <t>174750</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2016</t>
+          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2016 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>110432</t>
+          <t>111392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142556</t>
+          <t>142501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94843</t>
+          <t>96567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119646</t>
+          <t>120078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214897</t>
+          <t>214308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253426</t>
+          <t>253559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,34%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62264</t>
+          <t>61875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90991</t>
+          <t>90695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31397</t>
+          <t>32780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54363</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102060</t>
+          <t>102960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136552</t>
+          <t>138520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,82 +7241,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8161</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3274</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16216</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>22084</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>13721</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>34244</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>3,37%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8161</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3778</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17217</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>22084</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>13524</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>32985</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149728</t>
+          <t>147766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191345</t>
+          <t>191846</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137833</t>
+          <t>139463</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172475</t>
+          <t>171964</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>297035</t>
+          <t>298085</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>352070</t>
+          <t>349198</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113625</t>
+          <t>115391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153710</t>
+          <t>155539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61348</t>
+          <t>61614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92219</t>
+          <t>92199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185810</t>
+          <t>185939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237138</t>
+          <t>236001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58436</t>
+          <t>58316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91794</t>
+          <t>92144</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37731</t>
+          <t>37005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83283</t>
+          <t>82608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120469</t>
+          <t>121257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40906</t>
+          <t>41861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>24400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32687</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58757</t>
+          <t>57565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82779</t>
+          <t>81644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120142</t>
+          <t>119433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84389</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115308</t>
+          <t>114630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>177685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225261</t>
+          <t>225670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128805</t>
+          <t>128699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168167</t>
+          <t>167618</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94100</t>
+          <t>91962</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126702</t>
+          <t>125306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>229830</t>
+          <t>227242</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>283036</t>
+          <t>280684</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>60327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92085</t>
+          <t>92969</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63425</t>
+          <t>61073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>106697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146341</t>
+          <t>147885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24065</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40263</t>
+          <t>39511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69551</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>168928</t>
+          <t>170490</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>210310</t>
+          <t>209364</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180770</t>
+          <t>182025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>216195</t>
+          <t>217146</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>359422</t>
+          <t>364048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>416270</t>
+          <t>416978</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,71%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101973</t>
+          <t>102933</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>138723</t>
+          <t>139604</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65551</t>
+          <t>65786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97067</t>
+          <t>97607</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176150</t>
+          <t>177215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>227246</t>
+          <t>223129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49247</t>
+          <t>51310</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>79651</t>
+          <t>80680</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>42709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>77214</t>
+          <t>77257</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>116609</t>
+          <t>114182</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37388</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23109</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26174</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>51532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>548564</t>
+          <t>548910</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>629811</t>
+          <t>627082</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>529434</t>
+          <t>526256</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>592137</t>
+          <t>594592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1105975</t>
+          <t>1098877</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1199330</t>
+          <t>1199794</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>439029</t>
+          <t>438564</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>510898</t>
+          <t>511772</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>279690</t>
+          <t>278657</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>337047</t>
+          <t>341398</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>734765</t>
+          <t>740467</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>827450</t>
+          <t>828931</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209102</t>
+          <t>210538</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>266955</t>
+          <t>270349</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94959</t>
+          <t>96092</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133380</t>
+          <t>133533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317053</t>
+          <t>317854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>386287</t>
+          <t>386501</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86608</t>
+          <t>87609</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>127411</t>
+          <t>128215</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37931</t>
+          <t>38681</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66038</t>
+          <t>67529</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>133294</t>
+          <t>133186</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>184237</t>
+          <t>185336</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2023</t>
+          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48296</t>
+          <t>48626</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77724</t>
+          <t>77127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57213</t>
+          <t>58421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76867</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111349</t>
+          <t>111109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148918</t>
+          <t>147276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70434</t>
+          <t>72491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101650</t>
+          <t>102320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40479</t>
+          <t>40407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58588</t>
+          <t>58184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119296</t>
+          <t>118952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157191</t>
+          <t>155007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29295</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34804</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>178223</t>
+          <t>174601</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>477639</t>
+          <t>475580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85626</t>
+          <t>87051</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110578</t>
+          <t>111598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>288774</t>
+          <t>290362</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>625336</t>
+          <t>607747</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46766</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>262879</t>
+          <t>266459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66275</t>
+          <t>65807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88327</t>
+          <t>88281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85732</t>
+          <t>92678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>334053</t>
+          <t>332862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80192</t>
+          <t>82840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13445</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29888</t>
+          <t>28691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94497</t>
+          <t>96945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36083</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40882</t>
+          <t>39808</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62730</t>
+          <t>63006</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91988</t>
+          <t>92443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91122</t>
+          <t>93056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134497</t>
+          <t>137037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163135</t>
+          <t>163316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239425</t>
+          <t>230657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52702</t>
+          <t>52461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81949</t>
+          <t>80548</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57738</t>
+          <t>56563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>72723</t>
+          <t>75970</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>128378</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>28385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>33908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,82 +11456,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8684</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>16136</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>21654</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>12471</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>34430</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>3,7%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8684</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3865</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>16642</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>21654</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>11359</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>33788</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111059</t>
+          <t>110844</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142300</t>
+          <t>141526</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94290</t>
+          <t>95115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>119130</t>
+          <t>117754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>214481</t>
+          <t>212410</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>253160</t>
+          <t>253573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55282</t>
+          <t>54777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83009</t>
+          <t>84370</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>45935</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68499</t>
+          <t>67477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106864</t>
+          <t>107359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>143093</t>
+          <t>146124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29773</t>
+          <t>30405</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19930</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23573</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44828</t>
+          <t>44850</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,47 +12060,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>10,62%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>23061</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>15762</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>35267</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>23061</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>15464</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>34696</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>457677</t>
+          <t>455528</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>843744</t>
+          <t>827774</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>355537</t>
+          <t>357071</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>430236</t>
+          <t>440720</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>846687</t>
+          <t>846303</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1265604</t>
+          <t>1296034</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>187052</t>
+          <t>208227</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>474261</t>
+          <t>476780</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>186307</t>
+          <t>184475</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248871</t>
+          <t>247729</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>387149</t>
+          <t>378285</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>696494</t>
+          <t>700986</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48434</t>
+          <t>51272</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133335</t>
+          <t>133119</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53647</t>
+          <t>54688</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>88388</t>
+          <t>87723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>170905</t>
+          <t>172678</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21013</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67066</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>20777</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>98547</t>
+          <t>96869</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6601-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6601-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137885</t>
+          <t>136218</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176910</t>
+          <t>175776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93165</t>
+          <t>93831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117167</t>
+          <t>117199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237583</t>
+          <t>238914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284412</t>
+          <t>284999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75536</t>
+          <t>76257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110090</t>
+          <t>110031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29760</t>
+          <t>29567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52154</t>
+          <t>50706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114060</t>
+          <t>113636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153606</t>
+          <t>153993</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106364</t>
+          <t>105901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142582</t>
+          <t>143695</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114010</t>
+          <t>115140</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>154964</t>
+          <t>156381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>247280</t>
+          <t>246007</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>295252</t>
+          <t>295011</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177437</t>
+          <t>177316</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>207072</t>
+          <t>206844</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>435642</t>
+          <t>432415</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>493000</t>
+          <t>493616</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128587</t>
+          <t>127930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171109</t>
+          <t>169566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61379</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171455</t>
+          <t>169982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222859</t>
+          <t>223480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76981</t>
+          <t>77189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112437</t>
+          <t>112301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92011</t>
+          <t>91671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130473</t>
+          <t>130035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33713</t>
+          <t>34056</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>19848</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42274</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72998</t>
+          <t>73118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194886</t>
+          <t>197140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237385</t>
+          <t>238025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161816</t>
+          <t>161148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184158</t>
+          <t>183778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366042</t>
+          <t>367346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>414051</t>
+          <t>414438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77636</t>
+          <t>76191</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111200</t>
+          <t>111621</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22512</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42917</t>
+          <t>44218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,47 +2034,47 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>125174</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>105810</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>147067</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>20,24%</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>125174</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>106208</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>147117</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48205</t>
+          <t>49056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>78885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53320</t>
+          <t>52449</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83629</t>
+          <t>84153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24768</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46965</t>
+          <t>46243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25070</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48908</t>
+          <t>48461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>281341</t>
+          <t>280023</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>326027</t>
+          <t>327506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>288021</t>
+          <t>286264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>320569</t>
+          <t>319951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>578440</t>
+          <t>580166</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>637392</t>
+          <t>636541</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,43%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95947</t>
+          <t>95518</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133458</t>
+          <t>135437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39800</t>
+          <t>39571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65903</t>
+          <t>67435</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142829</t>
+          <t>144192</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>189540</t>
+          <t>191066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79557</t>
+          <t>79877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>116276</t>
+          <t>113772</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96600</t>
+          <t>97248</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>138482</t>
+          <t>136565</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31320</t>
+          <t>30795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>41273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69380</t>
+          <t>69565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>905606</t>
+          <t>901890</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>989497</t>
+          <t>996542</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>749087</t>
+          <t>752301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>804365</t>
+          <t>807122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1667353</t>
+          <t>1669857</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1779671</t>
+          <t>1780441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>412508</t>
+          <t>411167</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>486650</t>
+          <t>485374</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>147116</t>
+          <t>145802</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>193432</t>
+          <t>192637</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>572741</t>
+          <t>569504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>664860</t>
+          <t>667938</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>341730</t>
+          <t>341459</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>411617</t>
+          <t>412057</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69630</t>
+          <t>70374</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>395090</t>
+          <t>394576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>471829</t>
+          <t>473440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>113754</t>
+          <t>113374</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>158680</t>
+          <t>159975</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>34220</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>135220</t>
+          <t>134765</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>183921</t>
+          <t>184590</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85210</t>
+          <t>85581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117813</t>
+          <t>117878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81544</t>
+          <t>81484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107252</t>
+          <t>106740</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173729</t>
+          <t>173452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216711</t>
+          <t>214764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74138</t>
+          <t>73771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105397</t>
+          <t>105215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43485</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67909</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124439</t>
+          <t>124833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164110</t>
+          <t>165420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41219</t>
+          <t>40404</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67645</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18915</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50034</t>
+          <t>48753</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79503</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37663</t>
+          <t>38156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40364</t>
+          <t>39154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169395</t>
+          <t>170495</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>212182</t>
+          <t>211462</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>139451</t>
+          <t>138910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>171831</t>
+          <t>174011</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>320100</t>
+          <t>320316</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>374273</t>
+          <t>375979</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102540</t>
+          <t>101746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141745</t>
+          <t>140562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65726</t>
+          <t>65704</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98311</t>
+          <t>95975</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175459</t>
+          <t>174728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223952</t>
+          <t>226577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>53485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86105</t>
+          <t>83980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34404</t>
+          <t>34086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76446</t>
+          <t>75634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110603</t>
+          <t>111917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41111</t>
+          <t>40168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>20180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>29110</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56512</t>
+          <t>55402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129413</t>
+          <t>128180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167546</t>
+          <t>167897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119677</t>
+          <t>120465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149832</t>
+          <t>149952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257980</t>
+          <t>259570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308777</t>
+          <t>307133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85375</t>
+          <t>86741</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121864</t>
+          <t>123155</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65966</t>
+          <t>66517</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>135156</t>
+          <t>132965</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>179147</t>
+          <t>176622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>39161</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64614</t>
+          <t>66731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52309</t>
+          <t>51354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>83795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43126</t>
+          <t>42504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>170675</t>
+          <t>172053</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>210974</t>
+          <t>211492</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159118</t>
+          <t>156452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193705</t>
+          <t>192770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>336901</t>
+          <t>341056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>393573</t>
+          <t>396284</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98493</t>
+          <t>97556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136226</t>
+          <t>135300</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70531</t>
+          <t>69839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102322</t>
+          <t>103325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176753</t>
+          <t>177109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>226749</t>
+          <t>226867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65346</t>
+          <t>64729</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97852</t>
+          <t>95204</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31675</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>83015</t>
+          <t>82119</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>121863</t>
+          <t>121064</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20522</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42984</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65256</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>591739</t>
+          <t>589661</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>667742</t>
+          <t>669063</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>530004</t>
+          <t>531326</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>594378</t>
+          <t>592947</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1146174</t>
+          <t>1144741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1249935</t>
+          <t>1246569</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>396439</t>
+          <t>390243</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>464727</t>
+          <t>464612</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>245932</t>
+          <t>244687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>301053</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>657114</t>
+          <t>651151</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>748090</t>
+          <t>749621</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>225440</t>
+          <t>223220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>287031</t>
+          <t>287165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55300</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88292</t>
+          <t>88803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>290409</t>
+          <t>288561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>356099</t>
+          <t>358542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>84054</t>
+          <t>83222</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>128260</t>
+          <t>127030</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56233</t>
+          <t>56350</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>123764</t>
+          <t>124099</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>174750</t>
+          <t>172749</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111392</t>
+          <t>112846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142501</t>
+          <t>142109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96567</t>
+          <t>96586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120078</t>
+          <t>120512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214308</t>
+          <t>215495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253559</t>
+          <t>253896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61875</t>
+          <t>62245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90695</t>
+          <t>91593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32780</t>
+          <t>33162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102960</t>
+          <t>99416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138520</t>
+          <t>137103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>33871</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44279</t>
+          <t>44552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>15355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>149910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191846</t>
+          <t>190744</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>139463</t>
+          <t>139807</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>171964</t>
+          <t>172366</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>298085</t>
+          <t>299444</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>349198</t>
+          <t>352615</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115391</t>
+          <t>115092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155539</t>
+          <t>154531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61614</t>
+          <t>62278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92199</t>
+          <t>90993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>185153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236001</t>
+          <t>234502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>57886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92144</t>
+          <t>89703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>18004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82608</t>
+          <t>83418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121257</t>
+          <t>122462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41861</t>
+          <t>42240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31499</t>
+          <t>31175</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57565</t>
+          <t>58681</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81644</t>
+          <t>83357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119433</t>
+          <t>118842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84173</t>
+          <t>83058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114630</t>
+          <t>114418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177685</t>
+          <t>173813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225670</t>
+          <t>223931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128699</t>
+          <t>130533</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167618</t>
+          <t>164583</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91962</t>
+          <t>93066</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125306</t>
+          <t>124423</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>227242</t>
+          <t>231471</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>280684</t>
+          <t>281504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60327</t>
+          <t>60814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92969</t>
+          <t>93282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61073</t>
+          <t>62890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106697</t>
+          <t>106053</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147885</t>
+          <t>147362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52154</t>
+          <t>52012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23120</t>
+          <t>23516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39511</t>
+          <t>40366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69602</t>
+          <t>68605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>170490</t>
+          <t>170978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>209364</t>
+          <t>211394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>182025</t>
+          <t>178010</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>217146</t>
+          <t>216753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>364048</t>
+          <t>365276</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>416978</t>
+          <t>420744</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102933</t>
+          <t>100765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139604</t>
+          <t>137665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65786</t>
+          <t>65400</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97607</t>
+          <t>100183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177215</t>
+          <t>175632</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>223129</t>
+          <t>224452</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51310</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80680</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21469</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>42532</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>77257</t>
+          <t>78342</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>114182</t>
+          <t>113039</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34988</t>
+          <t>36895</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21823</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26411</t>
+          <t>26908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51532</t>
+          <t>53885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>548910</t>
+          <t>551362</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>627082</t>
+          <t>624785</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>526256</t>
+          <t>531320</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>594592</t>
+          <t>594450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1098877</t>
+          <t>1098310</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1199794</t>
+          <t>1197111</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>438564</t>
+          <t>438987</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>511772</t>
+          <t>510360</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>278657</t>
+          <t>280859</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>341398</t>
+          <t>337012</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>740467</t>
+          <t>738787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>828931</t>
+          <t>830201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>210538</t>
+          <t>209032</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>270349</t>
+          <t>265719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>96092</t>
+          <t>95121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133533</t>
+          <t>134658</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317854</t>
+          <t>315624</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>386501</t>
+          <t>383867</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>88936</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>128215</t>
+          <t>127762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38681</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>67529</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>133186</t>
+          <t>132056</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>185336</t>
+          <t>185082</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62069</t>
+          <t>74185</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48626</t>
+          <t>58380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77127</t>
+          <t>91095</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67156</t>
+          <t>75059</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58421</t>
+          <t>64978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77109</t>
+          <t>85673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>129225</t>
+          <t>149244</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111109</t>
+          <t>130404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147276</t>
+          <t>169427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86669</t>
+          <t>92789</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72491</t>
+          <t>75741</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102320</t>
+          <t>109676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>53469</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>44352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58184</t>
+          <t>63063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>136038</t>
+          <t>146258</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118952</t>
+          <t>127066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155007</t>
+          <t>166147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29461</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>24213</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>346429</t>
+          <t>114413</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174601</t>
+          <t>96681</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>475580</t>
+          <t>134721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98999</t>
+          <t>106518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87051</t>
+          <t>94162</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111598</t>
+          <t>119443</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445428</t>
+          <t>220930</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>290362</t>
+          <t>197385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>607747</t>
+          <t>246308</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>139632</t>
+          <t>152693</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48475</t>
+          <t>131866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>266459</t>
+          <t>173408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77103</t>
+          <t>84644</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65807</t>
+          <t>72920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88281</t>
+          <t>98068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>216736</t>
+          <t>237337</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92678</t>
+          <t>209574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332862</t>
+          <t>259982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39900</t>
+          <t>46999</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82840</t>
+          <t>62075</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>23050</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>16133</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28691</t>
+          <t>32499</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>60041</t>
+          <t>70048</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25398</t>
+          <t>55692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96945</t>
+          <t>88769</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39808</t>
+          <t>40120</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>76606</t>
+          <t>90897</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63006</t>
+          <t>74156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92443</t>
+          <t>109053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>110072</t>
+          <t>88232</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93056</t>
+          <t>77346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137037</t>
+          <t>98485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>186678</t>
+          <t>179129</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163316</t>
+          <t>159105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>230657</t>
+          <t>200156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65616</t>
+          <t>77698</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52461</t>
+          <t>59758</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80548</t>
+          <t>95602</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42230</t>
+          <t>51218</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56563</t>
+          <t>62432</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>107846</t>
+          <t>128916</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75970</t>
+          <t>109915</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>128378</t>
+          <t>148469</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>19109</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28385</t>
+          <t>33280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33908</t>
+          <t>38404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>126291</t>
+          <t>139332</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110844</t>
+          <t>122625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>141526</t>
+          <t>156145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>117671</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95115</t>
+          <t>105825</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117754</t>
+          <t>130939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>233852</t>
+          <t>257003</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>212410</t>
+          <t>235724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>253573</t>
+          <t>277471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>68388</t>
+          <t>75250</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54777</t>
+          <t>60356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84370</t>
+          <t>92472</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>56101</t>
+          <t>61104</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45935</t>
+          <t>50175</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67477</t>
+          <t>72684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>124489</t>
+          <t>136354</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107359</t>
+          <t>116848</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146124</t>
+          <t>156899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20179</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>31466</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>22377</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>36638</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>26545</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>49607</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35267</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>611395</t>
+          <t>418827</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>455528</t>
+          <t>386242</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>827774</t>
+          <t>457605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>383789</t>
+          <t>387480</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>357071</t>
+          <t>364753</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>440720</t>
+          <t>410496</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>995184</t>
+          <t>806308</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>846303</t>
+          <t>764440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1296034</t>
+          <t>853420</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>360305</t>
+          <t>398430</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>208227</t>
+          <t>364693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>476780</t>
+          <t>434970</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>224803</t>
+          <t>250436</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184475</t>
+          <t>229459</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>247729</t>
+          <t>272845</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>585108</t>
+          <t>648865</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>378285</t>
+          <t>608162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>700986</t>
+          <t>690532</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>96697</t>
+          <t>110165</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51272</t>
+          <t>90275</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133119</t>
+          <t>134557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>41164</t>
+          <t>48360</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54688</t>
+          <t>63803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>137861</t>
+          <t>158525</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87723</t>
+          <t>133904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>172678</t>
+          <t>183430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>44600</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>63546</t>
+          <t>70244</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>34102</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20777</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41230</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>74788</t>
+          <t>84937</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>67769</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>96869</t>
+          <t>107121</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
